--- a/阵营/的卢监控.xlsx
+++ b/阵营/的卢监控.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\阵营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9A617F11-1EC4-4732-A226-BE8C7EFEC458}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2BD761B6-781C-47DE-9E3C-B43F6B45301F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="1800" windowWidth="25110" windowHeight="12510" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="字典" sheetId="4" r:id="rId1"/>
@@ -21,9 +21,6 @@
     <sheet name="角色喊话" sheetId="10" r:id="rId6"/>
     <sheet name="系统频道" sheetId="11" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames>
     <definedName name="JunSun1" localSheetId="4">DATE(交互物件!日历年份,6,1)-WEEKDAY(DATE(交互物件!日历年份,6,1))</definedName>
     <definedName name="JunSun1" localSheetId="2">DATE(武学招式!日历年份,6,1)-WEEKDAY(DATE(武学招式!日历年份,6,1))</definedName>
@@ -55,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1562" uniqueCount="1273">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="1562" uniqueCount="1272">
   <si>
     <t>标识</t>
   </si>
@@ -3852,9 +3849,6 @@
   <si>
     <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="龙骧驰竞·消失模式",nTime=599.795,key="阵营活动",},</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,255,0,</t>
   </si>
   <si>
     <t>return {CASTING={</t>
@@ -4842,27 +4836,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="茗伊团队监控数据手册"/>
-      <sheetName val="字典"/>
-      <sheetName val="有利气劲"/>
-      <sheetName val="不利气劲"/>
-      <sheetName val="武学招式"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="Office 主题​​">
   <a:themeElements>
@@ -13176,10 +13149,10 @@
         <v>1156</v>
       </c>
       <c r="D1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F1" t="s">
         <v>1157</v>
@@ -13188,10 +13161,10 @@
         <v>1160</v>
       </c>
       <c r="H1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="I1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="J1" t="s">
         <v>1161</v>
@@ -13203,97 +13176,97 @@
         <v>1137</v>
       </c>
       <c r="M1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="N1" t="s">
         <v>1234</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1235</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>1236</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>1237</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>1238</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>1239</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>1240</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>1241</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>1242</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>1243</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>1244</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>1245</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>1246</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>1247</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>1248</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>1249</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>1250</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>1251</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>1252</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>1253</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>1254</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>1255</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>1256</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>1257</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>1258</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>1259</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>1260</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>1261</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>1262</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>1263</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>1264</v>
       </c>
       <c r="AR1" t="s">
         <v>1138</v>
@@ -13319,16 +13292,16 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="K3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="L3" t="s">
         <v>1265</v>
-      </c>
-      <c r="L3" t="s">
-        <v>1266</v>
       </c>
       <c r="S3">
         <v>1</v>
@@ -13340,16 +13313,16 @@
         <v>1</v>
       </c>
       <c r="AH3" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="AI3">
         <v>2</v>
       </c>
       <c r="AJ3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="AK3" t="s">
         <v>1267</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>1268</v>
       </c>
       <c r="AL3">
         <v>255</v>
@@ -13362,10 +13335,10 @@
         <v>{dwID=27490,nLevel=1,szName="驰踪令",nScrutinyType=1,szNote="抓捕的卢时不可选中",col={179,238,58,},[1]={bScreenHead=true,bBuffList=true,bTeamPanel=true,},[2]={},aCataclysmBuff={{szReminder="踪",nPriority=2,col="#B3EE3AFF",colScreenHead="#B3EE3A",nColAlpha=255,bScreenHead=true,},},tCountdown={{nClass=1,nIcon=4408,nFrame=6,nTime=20,szName="驰踪令·无法选中",key="驰踪令·专注",},{nClass=2,nIcon=4408,nFrame=5,nTime=0,szName="驰踪令·专注",key="驰踪令·专注",},},},</v>
       </c>
       <c r="AR3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="AS3" t="s">
         <v>1269</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.15">
@@ -13397,7 +13370,7 @@
         <v>1156</v>
       </c>
       <c r="D1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E1" t="s">
         <v>1157</v>
@@ -13406,10 +13379,10 @@
         <v>1160</v>
       </c>
       <c r="G1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="H1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="I1" t="s">
         <v>1161</v>
@@ -13421,46 +13394,46 @@
         <v>1137</v>
       </c>
       <c r="L1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="M1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="N1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="O1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="P1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="Q1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="R1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="S1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="T1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="U1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="V1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="W1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="X1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="Y1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="Z1" t="s">
         <v>1138</v>
@@ -13489,20 +13462,20 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>1207</v>
+        <v>1123</v>
       </c>
       <c r="V3">
         <v>1</v>
       </c>
       <c r="Y3" t="str">
         <f t="shared" ref="Y3:Y4" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(D3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(D2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nIcon="&amp;E3&amp;",","")&amp;IF(F3&lt;&gt;"","szName="""&amp;F3&amp;""",","")&amp;IF(G3&gt;0,"bCheckLevel=true"&amp;",","")&amp;IF(H3&gt;0,"nScrutinyType="&amp;H3&amp;",","")&amp;IF(I3&lt;&gt;"","tKungFu={"&amp;I3&amp;"},","")&amp;IF(J3&lt;&gt;"","szNote="""&amp;J3&amp;""",","")&amp;IF(K3&lt;&gt;"","col={"&amp;K3&amp;"},","")&amp;"[9]={"&amp;IF(L3&lt;&gt;"","tMark={"&amp;L3&amp;"},","")&amp;IF(M3&lt;&gt;"","szVoice="""&amp;M3&amp;""",","")&amp;IF(N3&gt;0,"bTeamChannel=true,","")&amp;IF(O3&gt;0,"bWhisperChannel=true,","")&amp;IF(P3&gt;0,"bCenterAlarm=true,","")&amp;IF(X3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;"[8]={"&amp;IF(Q3&lt;&gt;"","tMark={"&amp;Q3&amp;"},","")&amp;IF(R3&lt;&gt;"","szVoice="""&amp;R3&amp;""",","")&amp;IF(S3&gt;0,"bTeamChannel=true,","")&amp;IF(T3&gt;0,"bWhisperChannel=true,","")&amp;IF(U3&gt;0,"bCenterAlarm=true,","")&amp;IF(V3&gt;0,"bScreenHead=true,","")&amp;IF(W3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(Z3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,Z3:AAD3)&amp;"},","")&amp;"},")))</f>
-        <v>{dwID=7612,nLevel=1,nScrutinyType=1,col={0,255,0,},[9]={},[8]={bScreenHead=true,},tCountdown={{nClass=8,nIcon=3481,nFrame=4,nTime=10,szName="套马【{$receiver}】",key="套马",},{nClass=9,nIcon=3481,nFrame=4,nTime="30,套马·CD;32,套马·就绪",szName="套马·CD",nRefresh=0,key="套马",},},},</v>
+        <v>{dwID=7612,nLevel=1,nScrutinyType=1,col={0,255,255,},[9]={},[8]={bScreenHead=true,},tCountdown={{nClass=8,nIcon=3481,nFrame=4,nTime=10,szName="套马【{$receiver}】",key="套马",},{nClass=9,nIcon=3481,nFrame=4,nTime="30,套马·CD;32,套马·就绪",szName="套马·CD",nRefresh=0,key="套马",},},},</v>
       </c>
       <c r="Z3" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="AA3" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.15">
@@ -13844,7 +13817,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B2">
         <v>330</v>
@@ -13856,13 +13829,13 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="C3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D3" t="s">
         <v>1226</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>1227</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1228</v>
       </c>
       <c r="F3" t="s">
         <v>1155</v>
@@ -13872,7 +13845,7 @@
         <v>{szContent="龙骧驰竞活动在即，为公平起见，侠士将在30秒后被传出本图，活动排队将在21：10分正式开始，请做好准备。",szTarget="%",szNote="龙骧驰竞·清图离开",col={255,255,100,},[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="龙骧驰竞·清图传送",nTime="30,龙骧驰竞·的卢·传送剩余;32,龙骧驰竞·的卢·清图传送",nRefresh=1,key="挂机检测",},},},</v>
       </c>
       <c r="P3" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
@@ -14057,7 +14030,7 @@
         <v>1198</v>
       </c>
       <c r="P7" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
@@ -14090,7 +14063,7 @@
         <v>1199</v>
       </c>
       <c r="P8" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.15">

--- a/阵营/的卢监控.xlsx
+++ b/阵营/的卢监控.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="字典" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="日历年份" localSheetId="4">#REF!</definedName>
     <definedName name="日历年份" localSheetId="1">#REF!</definedName>
     <definedName name="日历年份">#REF!</definedName>
-    <definedName name="JunSun1" localSheetId="2">DATE(不利气劲!日历年份,6,1)-WEEKDAY(DATE(不利气劲!日历年份,6,1))</definedName>
+    <definedName name="JunSun1" localSheetId="2">DATE(日历年份,6,1)-WEEKDAY(DATE(日历年份,6,1))</definedName>
     <definedName name="日历年份" localSheetId="2">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -3794,16 +3794,52 @@
     <t>通用的数据</t>
   </si>
   <si>
+    <t>龙骧驰竞排队正式开始，侠士们速速前往龙泉府地图参与排队。\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=5815,nFrame=-1,szName="的卢·龙泉府·开始排队",nTime="1,的卢·龙泉府·开始排队;10,的卢·龙泉府·开始排队;60,的卢·龙泉府·等待排队",nRefresh=1,key="阵营活动",},</t>
+  </si>
+  <si>
     <t>龙骧驰竞即将开始，为防弄虚作假者，即将对“龙泉府”地图进行清场操作，并在“21：10”开始排队，请勿在21：10前排队，将被视为无效，请侠士们提前做好准备。\n</t>
   </si>
   <si>
     <t>{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="龙骧驰竞·消失模式",nTime=599.795,key="阵营活动",},</t>
   </si>
   <si>
-    <t>龙骧驰竞排队正式开始，侠士们速速前往龙泉府地图参与排队。\n</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=5815,nFrame=-1,szName="的卢·龙泉府·开始排队",nTime="1,的卢·龙泉府·开始排队;10,的卢·龙泉府·开始排队;60,的卢·龙泉府·等待排队",nRefresh=1,key="阵营活动",},</t>
+    <t>的卢已经出现在龙泉府中，浩气盟和恶人谷的侠士可前去尝试抓捕！\n</t>
+  </si>
+  <si>
+    <t>龙泉府·的卢·出山</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=21034,nFrame=8,szName="的卢·保护剩余",nTime="600,的卢·保护剩余;610,的卢·保护结束",nRefresh=1,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>^江湖快马飞报！恶人谷侠士“(.-)”在龙泉府捕获(%d-)级稀有坐骑[马]-“(.-)”</t>
+  </si>
+  <si>
+    <t>恶人谷·[{$1}]·捕获·{$3}</t>
+  </si>
+  <si>
+    <t>255,100,100,</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=21034,nFrame=3,szName="恶人谷[{$1}]捕获·{$3}",nTime=60,key="阵营活动",},</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=13,nTime=-1,szName="套马",key="套马",},</t>
+  </si>
+  <si>
+    <t>^江湖快马飞报！浩气盟侠士“(.-)”在龙泉府捕获(%d-)级稀有坐骑[马]-“(.-)”</t>
+  </si>
+  <si>
+    <t>浩气盟·[{$1}]·捕获·{$3}</t>
+  </si>
+  <si>
+    <t>100,100,255,</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=21034,nFrame=7,szName="浩气盟[{$1}]捕获·{$3}",nTime=60,key="阵营活动",},</t>
   </si>
   <si>
     <t>^江湖快马飞报！(.-)侠士“(.-)”在龙泉府捕获(%d-)级稀有坐骑[马]-“(.-)”</t>
@@ -3813,42 +3849,6 @@
   </si>
   <si>
     <t>{nClass=20,nIcon=21034,nFrame=8,szName="{$1}[{$2}]捕获·{$4}",nTime=60,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>^江湖快马飞报！恶人谷侠士“(.-)”在龙泉府捕获(%d-)级稀有坐骑[马]-“(.-)”</t>
-  </si>
-  <si>
-    <t>恶人谷·[{$1}]·捕获·{$3}</t>
-  </si>
-  <si>
-    <t>255,100,100,</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=21034,nFrame=3,szName="恶人谷[{$1}]捕获·{$3}",nTime=60,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=13,nTime=-1,szName="套马",key="套马",},</t>
-  </si>
-  <si>
-    <t>^江湖快马飞报！浩气盟侠士“(.-)”在龙泉府捕获(%d-)级稀有坐骑[马]-“(.-)”</t>
-  </si>
-  <si>
-    <t>浩气盟·[{$1}]·捕获·{$3}</t>
-  </si>
-  <si>
-    <t>100,100,255,</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=21034,nFrame=7,szName="浩气盟[{$1}]捕获·{$3}",nTime=60,key="阵营活动",},</t>
-  </si>
-  <si>
-    <t>的卢已经出现在龙泉府中，浩气盟和恶人谷的侠士可前去尝试抓捕！\n</t>
-  </si>
-  <si>
-    <t>龙泉府·的卢·出山</t>
-  </si>
-  <si>
-    <t>{nClass=20,nIcon=21034,nFrame=8,szName="的卢·保护剩余",nTime="600,的卢·保护剩余;610,的卢·保护结束",nRefresh=1,key="阵营活动",},</t>
   </si>
 </sst>
 </file>
@@ -13315,7 +13315,6 @@
       <c r="K3" t="s">
         <v>1182</v>
       </c>
-      <c r="L3"/>
       <c r="AQ3" t="str">
         <f>IF(B3&lt;&gt;"",IF(IFERROR(VALUE(C2),0)&lt;=0,"["&amp;B3&amp;"]={","},["&amp;B3&amp;"]={"),IF(C3&gt;0,"{dwID="&amp;C3&amp;","&amp;"nLevel="&amp;D3&amp;","&amp;IF(E3&gt;0,"nCount="&amp;E3&amp;",","")&amp;IF(F3&gt;0,"nIcon="&amp;F3&amp;",","")&amp;IF(G3&lt;&gt;"","szName="""&amp;G3&amp;""",","")&amp;IF(H3&gt;0,"bCheckLevel=true,","")&amp;IF(I3&gt;0,"nScrutinyType="&amp;I3&amp;",","")&amp;IF(J3&lt;&gt;"","tKungFu={"&amp;J3&amp;"},","")&amp;IF(K3&lt;&gt;"","szNote="""&amp;K3&amp;""",","")&amp;IF(L3&lt;&gt;"","col={"&amp;L3&amp;"},","")&amp;"[1]={"&amp;IF(M3&lt;&gt;"","tMark={"&amp;M3&amp;"},","")&amp;IF(N3&lt;&gt;"","szVoice="""&amp;N3&amp;""",","")&amp;IF(O3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(P3&gt;0,"bTeamChannel=true,","")&amp;IF(Q3&gt;0,"bWhisperChannel=true,","")&amp;IF(R3&gt;0,"bCenterAlarm=true,","")&amp;IF(S3&gt;0,"bScreenHead=true,","")&amp;IF(T3&gt;0,"bPartyBuffList=true,","")&amp;IF(U3&gt;0,"bBuffList=true,","")&amp;IF(V3&gt;0,"bFullScreen=true,","")&amp;IF(W3&gt;0,"bTeamPanel=true,","")&amp;IF(X3&gt;0,"bOnlySelfSrc=true,","")&amp;"},"&amp;"[2]={"&amp;IF(Y3&lt;&gt;"","szVoice="""&amp;Y3&amp;""",","")&amp;IF(Z3&gt;0,"bVoiceSelfOnly=true,","")&amp;IF(AA3&gt;0,"bTeamChannel=true,","")&amp;IF(AB3&gt;0,"bWhisperChannel=true,","")&amp;IF(AC3&gt;0,"bCenterAlarm=true,","")&amp;"},"&amp;IF(OR(AD3&gt;0,AH3&lt;&gt;"",AI3&gt;0,AJ3&lt;&gt;"",AK3&lt;&gt;"",AL3&gt;0,AM3&gt;0,AN3&gt;0,AO3&gt;0),"aCataclysmBuff={{"&amp;IF(AD3&gt;0,"nStackNum="&amp;AD3&amp;",","")&amp;IF(AE3&lt;&gt;"","szStackOp="""&amp;AE3&amp;""",","")&amp;IF(AF3&gt;0,"bOnlyMine=true,","")&amp;IF(AG3&gt;0,"bOnlyMe=true,","")&amp;IF(AH3&lt;&gt;"","szReminder="""&amp;AH3&amp;""",","")&amp;IF(AI3&gt;0,"nPriority="&amp;AI3&amp;",","")&amp;IF(AJ3&lt;&gt;"","col="""&amp;AJ3&amp;""",","")&amp;IF(AK3&lt;&gt;"","colScreenHead="""&amp;AK3&amp;""",","")&amp;IF(AL3&gt;0,"nColAlpha="&amp;AL3&amp;",","")&amp;IF(AM3&gt;0,"bAttention=true,","")&amp;IF(AN3&gt;0,"bCaution=true,","")&amp;IF(AO3&gt;0,"bScreenHead=true,","")&amp;"},"&amp;AP3&amp;"},","")&amp;IF(AR3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,AR3:AAC3)&amp;"},","")&amp;"},",IF(C2&gt;0,"},","")&amp;IF(AND(B3="",C3="",OR(B2&lt;&gt;"",C2&lt;&gt;"")),"},}","")))</f>
         <v>{dwID=26817,nLevel=1,nScrutinyType=1,szNote="勇武",[1]={},[2]={},},</v>
@@ -13922,7 +13921,7 @@
       </c>
       <c r="N3" t="str">
         <f t="shared" ref="N3:N10" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="龙骧驰竞即将开始，为防弄虚作假者，即将对“龙泉府”地图进行清场操作，并在“21：10”开始排队，请勿在21：10前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="龙骧驰竞·消失模式",nTime=599.795,key="阵营活动",},},},</v>
+        <v>{szContent="龙骧驰竞排队正式开始，侠士们速速前往龙泉府地图参与排队。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="的卢·龙泉府·开始排队",nTime="1,的卢·龙泉府·开始排队;10,的卢·龙泉府·开始排队;60,的卢·龙泉府·等待排队",nRefresh=1,key="阵营活动",},},},</v>
       </c>
       <c r="O3" t="s">
         <v>1249</v>
@@ -13937,7 +13936,7 @@
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="龙骧驰竞排队正式开始，侠士们速速前往龙泉府地图参与排队。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=5815,nFrame=-1,szName="的卢·龙泉府·开始排队",nTime="1,的卢·龙泉府·开始排队;10,的卢·龙泉府·开始排队;60,的卢·龙泉府·等待排队",nRefresh=1,key="阵营活动",},},},</v>
+        <v>{szContent="龙骧驰竞即将开始，为防弄虚作假者，即将对“龙泉府”地图进行清场操作，并在“21：10”开始排队，请勿在21：10前排队，将被视为无效，请侠士们提前做好准备。\n",col={255,255,100,},[20]={},tCountdown={{nClass=20,nIcon=1465,nFrame=-1,bHold=true,szName="龙骧驰竞·消失模式",nTime=599.795,key="阵营活动",},},},</v>
       </c>
       <c r="O4" t="s">
         <v>1251</v>
@@ -13965,12 +13964,6 @@
       <c r="E6" t="s">
         <v>235</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
       <c r="K6">
         <v>1</v>
       </c>
@@ -13979,7 +13972,7 @@
       </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="^江湖快马飞报！(.-)侠士“(.-)”在龙泉府捕获(%d-)级稀有坐骑[马]-“(.-)”",szNote="{$1}[{$2}]·捕获·{$4}",col={255,255,255,},bReg=true,[20]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=21034,nFrame=8,szName="{$1}[{$2}]捕获·{$4}",nTime=60,key="阵营活动",},},},</v>
+        <v>{szContent="的卢已经出现在龙泉府中，浩气盟和恶人谷的侠士可前去尝试抓捕！\n",szNote="龙泉府·的卢·出山",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=21034,nFrame=8,szName="的卢·保护剩余",nTime="600,的卢·保护剩余;610,的卢·保护结束",nRefresh=1,key="阵营活动",},},},</v>
       </c>
       <c r="O6" t="s">
         <v>1254</v>
@@ -14061,6 +14054,12 @@
       <c r="E9" t="s">
         <v>235</v>
       </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
       <c r="K9">
         <v>1</v>
       </c>
@@ -14069,7 +14068,7 @@
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="的卢已经出现在龙泉府中，浩气盟和恶人谷的侠士可前去尝试抓捕！\n",szNote="龙泉府·的卢·出山",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=21034,nFrame=8,szName="的卢·保护剩余",nTime="600,的卢·保护剩余;610,的卢·保护结束",nRefresh=1,key="阵营活动",},},},</v>
+        <v>{szContent="^江湖快马飞报！(.-)侠士“(.-)”在龙泉府捕获(%d-)级稀有坐骑[马]-“(.-)”",szNote="{$1}[{$2}]·捕获·{$4}",col={255,255,255,},bReg=true,[20]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=21034,nFrame=8,szName="{$1}[{$2}]捕获·{$4}",nTime=60,key="阵营活动",},},},</v>
       </c>
       <c r="O9" t="s">
         <v>1266</v>
